--- a/data/specs/sample_filled.xlsx
+++ b/data/specs/sample_filled.xlsx
@@ -560,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -712,80 +712,82 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Additional required headers</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Client-Id: claims-intake-app-4f21
+X-Api-Version: 2026-03-01</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Header-Name: value, one per line. Sent on every request, whether or not authentication is used. These are literal values written as-is - they are not extracted from anywhere and are not resolved from secrets. Never put a secret or key value here; list it under Credential reference names instead.</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Client-Id: your-app-client-id
+X-Api-Version: 2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Authentication</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Auth type</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>OAuth2 client credentials</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Pick from the dropdown.</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>OAuth2 client credentials</t>
-        </is>
-      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Token endpoint URL</t>
+          <t>Auth type</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>https://sso.example.internal/connect/token</t>
+          <t>OAuth2 client credentials</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>If auth used</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Full URL of the call that issues the token.</t>
+          <t>Pick from the dropdown.</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>https://auth.example.internal/oauth2/token</t>
+          <t>OAuth2 client credentials</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Token request method</t>
+          <t>Token endpoint URL</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>https://sso.example.internal/connect/token</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -795,24 +797,24 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Pick from the dropdown.</t>
+          <t>Full URL of the call that issues the token.</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>https://auth.example.internal/oauth2/token</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Token request content type</t>
+          <t>Token request method</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>application/x-www-form-urlencoded</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -822,39 +824,66 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>e.g. application/x-www-form-urlencoded or application/json</t>
+          <t>Pick from the dropdown.</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>application/x-www-form-urlencoded</t>
+          <t>POST</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
+          <t>Token request content type</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>application/x-www-form-urlencoded</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>If auth used</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>e.g. application/x-www-form-urlencoded or application/json</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>application/x-www-form-urlencoded</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
           <t>Token request parameters</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>grant_type
 client_id
 client_secret</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>If auth used</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>Parameter names only, never values. One per line.</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>grant_type
 client_id
@@ -863,67 +892,40 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Token lifetime (seconds)</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>3600</v>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>How long a token stays valid. Used to decide whether a long test needs to refresh it mid-run.</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>3600</t>
-        </is>
-      </c>
-    </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Auth header name</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Authorization</t>
-        </is>
+          <t>Token lifetime (seconds)</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>3600</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>If auth used</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>The header the token is sent in on every later call.</t>
+          <t>How long a token stays valid. Used to decide whether a long test needs to refresh it mid-run.</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Authorization</t>
+          <t>3600</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Auth header value format</t>
+          <t>Auth header name</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Bearer {token}</t>
+          <t>Authorization</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -933,73 +935,100 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Use {token} as the placeholder.</t>
+          <t>The header the token is sent in on every later call.</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Bearer {token}</t>
+          <t>Authorization</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
+          <t>Auth header value format</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Bearer {token}</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>If auth used</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Use {token} as the placeholder.</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Bearer {token}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
           <t>Credential reference names</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>claims-perf-id
 claims-perf-secret</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>If auth used</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>Secret names only, never the secret values themselves. One per line.</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>perf-client-id
 perf-client-secret</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Account model</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Single shared</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>Single shared means one token is fetched once and reused by every virtual user. One per user means each virtual user logs in separately.</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Single shared</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Never type a password, secret or key into this workbook. Enter the name the secret is stored under and the framework retrieves the value at run time.</t>
         </is>
@@ -1007,16 +1036,16 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A20:E20"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"None,OAuth2 client credentials,OAuth2 password,OAuth2 PKCE,Bearer static,API key,Basic"</formula1>
     </dataValidation>
-    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"POST,GET"</formula1>
     </dataValidation>
-    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Single shared,One per user"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/specs/sample_filled.xlsx
+++ b/data/specs/sample_filled.xlsx
@@ -9,10 +9,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flows" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flow steps" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Load profiles" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLA" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auth flow steps" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flows" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flow steps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Load profiles" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLA" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -514,24 +515,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B6"/>
+  <dimension ref="B2:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="104" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="86" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>API performance test specification — filled sample</t>
+          <t>API performance test specification - filled sample</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>A complete worked example. Use it to see what a finished specification looks like, and as a reference while filling in the blank template.</t>
+          <t>A complete worked example, using OAuth2 client credentials. Use it to see what a finished specification looks like.</t>
         </is>
       </c>
     </row>
@@ -546,6 +547,13 @@
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Do not edit this file and submit it. Fill in the blank template instead. The values here describe an imaginary service and will not work against anything.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>This example does not use PKCE, so the PKCE only fields on the Application sheet and the whole Auth flow steps sheet are left blank - which is exactly what a non-PKCE specification should look like.</t>
         </is>
       </c>
     </row>
@@ -560,13 +568,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -653,7 +661,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Scheme and host, no trailing slash.</t>
+          <t>Scheme and host of the API under test, no trailing slash.</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
@@ -695,7 +703,7 @@
           <t>API reference location</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr"/>
+      <c r="B6" s="8" t="n"/>
       <c r="C6" s="9" t="inlineStr">
         <is>
           <t>No</t>
@@ -712,7 +720,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="44" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Additional required headers</t>
@@ -731,7 +739,7 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Header-Name: value, one per line. Sent on every request, whether or not authentication is used. These are literal values written as-is - they are not extracted from anywhere and are not resolved from secrets. Never put a secret or key value here; list it under Credential reference names instead.</t>
+          <t>Header-Name: value, one per line. Sent on every request, whether or not authentication is used. Literal values written as-is - never resolved from secrets. Never put a secret or key value here; list it under Credential reference names instead.</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -752,7 +760,7 @@
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="44" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Auth type</t>
@@ -770,7 +778,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Pick from the dropdown.</t>
+          <t>Pick from the dropdown. Which of the fields below you need depends on this - see the Read me.</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -792,7 +800,7 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>If auth used</t>
+          <t>Most types</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -819,7 +827,7 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>If auth used</t>
+          <t>Most types</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -846,7 +854,7 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>If auth used</t>
+          <t>Most types</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
@@ -875,7 +883,7 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>If auth used</t>
+          <t>Most types</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
@@ -892,7 +900,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="14" ht="44" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Token lifetime (seconds)</t>
@@ -1000,7 +1008,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
+    <row r="18" ht="44" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Account model</t>
@@ -1018,7 +1026,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>Single shared means one token is fetched once and reused by every virtual user. One per user means each virtual user logs in separately.</t>
+          <t>Single shared means one token is fetched once and reused by every virtual user. One per user means each virtual user authenticates separately.</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -1027,16 +1035,142 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Never type a password, secret or key into this workbook. Enter the name the secret is stored under and the framework retrieves the value at run time.</t>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>PKCE only</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Authorize endpoint URL</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>PKCE only</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Full URL. Any tenant or realm identifier lives inside this path - there is no separate field.</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>https://login.example.com/&lt;tenant&gt;/oauth2/v2.0/authorize</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Redirect URI</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>PKCE only</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Must match what is registered with the identity provider, exactly. Ask whoever owns the app registration.</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>msal&lt;client-id&gt;://auth</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>PKCE only</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Space-separated if there is more than one.</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>api://example.com/service/Execute</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="44" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Seed cookies</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Name: value per line. Only needed if the identity provider expects cookies to be present before the flow starts.</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>AADSSO: NA|NoExtension</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Seed cookie domain</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>If seed cookies</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Domain the seed cookies belong to.</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>login.example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="44" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Never type a password, secret or key into this workbook. Enter the name the secret is stored under and the framework retrieves the value at run time. Which fields you need depends on your Auth type - see the Read me.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A26:E26"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -1059,6 +1193,188 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Step no</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Step name</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Endpoint path</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Request body or parameters</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Request headers</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Expected status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n"/>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>ONLY used when Auth type is OAuth2 PKCE. Leave this sheet completely blank for every other auth type. These are the login calls that happen between the authorize call and the token call - the sequence a browser would normally walk through. The last step is the one that produces the authorization code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Two kinds of placeholder are supported here. {secret:name} is resolved from the environment at run time - use it for the login username and password, never a literal. {name} is a value the framework discovers from an earlier response and correlates for you. Do not list the PKCE parameters themselves (response_type, client_id, scope, redirect_uri, code_challenge, code_challenge_method) - those are added automatically from the Application sheet.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A16:G16"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"GET,POST,PUT,PATCH,DELETE"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1142,7 +1458,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="40" customHeight="1">
+    <row r="5" ht="44" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Share of load must total 100 across all flows. Safe to run means the framework is allowed to call this flow once while building the script. Answer No for anything that creates, changes or deletes real data you cannot afford to have written.</t>
@@ -1162,22 +1478,23 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1213,6 +1530,11 @@
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
+          <t>Request headers</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
           <t>Expected status</t>
         </is>
       </c>
@@ -1242,7 +1564,8 @@
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr"/>
-      <c r="G2" s="8" t="n">
+      <c r="G2" s="8" t="inlineStr"/>
+      <c r="H2" s="8" t="n">
         <v>200</v>
       </c>
     </row>
@@ -1271,7 +1594,8 @@
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr"/>
-      <c r="G3" s="8" t="n">
+      <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="8" t="n">
         <v>200</v>
       </c>
     </row>
@@ -1304,7 +1628,8 @@
           <t>{"type":"standard","subject":"Load test"}</t>
         </is>
       </c>
-      <c r="G4" s="8" t="n">
+      <c r="G4" s="8" t="inlineStr"/>
+      <c r="H4" s="8" t="n">
         <v>201</v>
       </c>
     </row>
@@ -1333,20 +1658,21 @@
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="n">
         <v>200</v>
       </c>
     </row>
-    <row r="7" ht="40" customHeight="1">
+    <row r="7" ht="44" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>Steps run in the order numbered. Use {name} in a path for any value that comes back from an earlier call — the framework works out where it comes from and wires it in. Query parameters can be written straight into the endpoint path. Content type is inferred from the request body.</t>
+          <t>Steps run in the order numbered. Use {name} in a path, body or header for any value that comes back from an earlier call - the framework works out where it comes from and wires it in. Request headers is Header-Name: value, one per line. The authentication header is added automatically - do not list it here.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A7:H7"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="D2:D5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -1357,7 +1683,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1516,10 +1842,10 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="40" customHeight="1">
+    <row r="7" ht="44" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>Fill in concurrent users, target throughput, or both. Users alone sets the number of virtual users. Adding a throughput target also holds the test to that rate as response times change. If a test is marked Required and both are blank, the framework stops and tells you rather than choosing a number for you. Endurance is usually quoted in hours — convert to minutes.</t>
+          <t>Fill in concurrent users, target throughput, or both. If a test is marked Required and both are blank, the framework stops and tells you rather than choosing a number for you. Endurance is usually quoted in hours - convert to minutes.</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1865,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1636,7 +1962,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="40" customHeight="1">
+    <row r="6" ht="44" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Applies to is either a Flow ID from the Flows sheet or the words All flows. These targets are written to a separate pass/fail file rather than into the script itself, because checking response times inside the script would count slow-but-successful calls as failures and distort the results.</t>
